--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-08T05:37:29.947Z</t>
+    <t>2026-04-08T05:42:24.897Z</t>
   </si>
   <si>
     <t>Pharmaceutical Research &amp; Development | AbbVie</t>
